--- a/uat-test-plans-reduced30/G2-16283-colour-linking.xlsx
+++ b/uat-test-plans-reduced30/G2-16283-colour-linking.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[Reduced ~25% — 6/8 checks retained, lowest-priority sections dropped] 4 UI-testable child stories mapped to 8 business checklist checks and 8 coverage rows. 8 child items were excluded as backend-only, spike, or technical non-business execution scope.</t>
+          <t>[Reduced V2 ~12% — 7/8 checks retained; AC and core-case coverage guardrails enforced] 4 UI-testable child stories mapped to 8 business checklist checks and 8 coverage rows. 8 child items were excluded as backend-only, spike, or technical non-business execution scope.</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>payload_bytes=10117; payload_chars=10115; est_tokens~2529; checklist_rows=6; matrix_rows=6; exploratory_rows=3</t>
+          <t>payload_bytes=11313; payload_chars=11311; est_tokens~2828; checklist_rows=7; matrix_rows=8; exploratory_rows=3</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -797,10 +797,10 @@
       <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr"/>
     </row>
-    <row r="3" ht="79" customHeight="1">
+    <row r="3" ht="64" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>UAT-002</t>
+          <t>UAT-003</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -810,136 +810,135 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Color Switching</t>
+          <t>A2B and A2W</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Switch MiniPDP color swatches and verify image and size-state updates</t>
+          <t>Validate add-to-bag and add-to-wishlist actions after color change</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>In MiniPDP, choose a different color swatch and observe image refresh and size availability state changes.</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>Selected swatch updates the active product image.
-Size availability reflects selected color state.
-MiniPDP remains open during color switching.</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4" ht="64" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>UAT-003</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Kozlova, Nika || External</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>A2B and A2W</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Validate add-to-bag and add-to-wishlist actions after color change</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>1. After selecting a new color and size, add to bag
 2. repeat add-to-wishlist into selected list and observe duplicate handling.</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Add-to-bag succeeds for available size.
 Add-to-wishlist applies to selected list.
 Duplicate-add attempt displays expected warning without state corruption.</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5" ht="79" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr"/>
+      <c r="H3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4" ht="79" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>UAT-004</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Kozlova, Nika || External</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>PDP Swatch Rendering</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Verify alternative color selector renders on PDP</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>1. Open PDP items with one, two, and many colors
 2. verify swatch list visibility and selected-state indicator.</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Alternative color selector is visible for applicable items.
 Selected swatch has clear active indicator.
 Single-color and multi-color cases render consistently.</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="79" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="79" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>UAT-005</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Kozlova, Nika || External</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Horizontal Scroll</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Use vertical mouse wheel to horizontally scroll color picker on desktop</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>On desktop PDP where swatches overflow viewport width, use vertical wheel while pointer is over swatch rail.</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Swatch rail moves horizontally with vertical wheel input.
 User can reach off-screen swatches without auxiliary devices.
 Interaction remains smooth without freeze.</t>
         </is>
       </c>
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="64" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>UAT-006</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Kozlova, Nika || External</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Cross-Brand Behavior</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Confirm color-selection behavior parity on NAP and MRP acceptance</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Repeat key MiniPDP/PDP swatch flows on both brand acceptance environments and compare outcomes.</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Core color interaction behavior is equivalent across brands.
+No brand-specific blocker appears in basic selection flow.</t>
+        </is>
+      </c>
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
     </row>
@@ -979,6 +978,43 @@
       </c>
       <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="79" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>UAT-008</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Kozlova, Nika || External</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Data Robustness</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Exercise products with different color-count datasets</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>1. Use acceptance products covering one, two, three, and many-color scenarios from Jira test notes
+2. execute core color-switch journey.</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>All sample datasets are navigable.
+No broken swatch state appears for higher color counts.
+Journey remains stable for color and size selection.</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -991,7 +1027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -999,11 +1035,11 @@
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -1092,7 +1128,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>UAT-001, UAT-002</t>
+          <t>UAT-001</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -1149,7 +1185,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>UAT-001, UAT-002, UAT-003</t>
+          <t>UAT-001, UAT-003</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1333,58 +1369,164 @@
       </c>
       <c r="K6" s="5" t="inlineStr"/>
     </row>
-    <row r="7" ht="49" customHeight="1">
+    <row r="7" ht="19" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
+          <t>COV-006</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>G2-18366</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>AC-CROSS-BRAND</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Cross-brand execution on NAP and MRP</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>UAT-006</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Jira AC explicitly references NAP and MRP.</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="49" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
           <t>COV-007</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>G2-18366,G2-21838</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>AC-RESPONSIVE</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Desktop and mobile interaction parity for swatches</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>UAT-007</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Desktop/mobile notes in Jira AC and test comments; no dedicated mobile-specific implementation ticket surfaced in this epic map.</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>UX</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>COV-008</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>G2-19715,G2-21838</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>AC-DATASET-ROBUSTNESS</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Color picker stability across variable color-count products</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>UAT-008</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Jira comments include acceptance test products with different color counts.</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/uat-test-plans-reduced30/G2-16283-colour-linking.xlsx
+++ b/uat-test-plans-reduced30/G2-16283-colour-linking.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[Reduced V2 ~12% — 7/8 checks retained; AC and core-case coverage guardrails enforced] 4 UI-testable child stories mapped to 8 business checklist checks and 8 coverage rows. 8 child items were excluded as backend-only, spike, or technical non-business execution scope.</t>
+          <t>[Reduced V2 ~12% — 7/8 checks retained; AC coverage guardrail enforced] 4 UI-testable child stories mapped to 8 business checklist checks and 8 coverage rows. 8 child items were excluded as backend-only, spike, or technical non-business execution scope.</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>payload_bytes=11313; payload_chars=11311; est_tokens~2828; checklist_rows=7; matrix_rows=8; exploratory_rows=3</t>
+          <t>payload_bytes=11298; payload_chars=11296; est_tokens~2824; checklist_rows=7; matrix_rows=8; exploratory_rows=3</t>
         </is>
       </c>
     </row>
